--- a/results/Int Task Remove ACC 0.2/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0007456692240171315</v>
+        <v>-0.0008253795283466181</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.002621054146086528</v>
+        <v>-0.0009113639008579887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001473584644490146</v>
+        <v>-0.0002457789594866134</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0003344061114412898</v>
+        <v>9.627896201303671e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.001717068448543876</v>
+        <v>-9.574594124989507e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001853189216413764</v>
+        <v>0.001794254894503119</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0001242458266199864</v>
+        <v>-7.648977679974867e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002018922465103042</v>
+        <v>-0.000189232128713004</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01069142474355525</v>
+        <v>0.01108748810521818</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008617953010863389</v>
+        <v>0.009689626728424543</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001359648294905316</v>
+        <v>-0.0009695619476469342</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.003810224519099727</v>
+        <v>0.0001962691364197178</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0003349856091408299</v>
+        <v>0.002160613675628197</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01453526478514825</v>
+        <v>0.009045318933946856</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005558398788747039</v>
+        <v>0.004491816627174637</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002894621783557283</v>
+        <v>0.0001437616692956369</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001793979836048575</v>
+        <v>0.0001848175911446371</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.00216995470983097</v>
+        <v>-0.001795848511553765</v>
       </c>
       <c r="U3" t="n">
-        <v>6.036036040607536e-05</v>
+        <v>0.0004672327096155226</v>
       </c>
       <c r="V3" t="n">
-        <v>-8.710082259577596e-06</v>
+        <v>1.839660503588635e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005416536165860767</v>
+        <v>0.00159935839132168</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0006076818148960507</v>
+        <v>-0.0004091264303244845</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0003790252112560664</v>
+        <v>0.0001483338912881238</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.923068100538209e-06</v>
+        <v>0.0008266083528036372</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.001002518541182075</v>
+        <v>-0.0002022627834074863</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0004106149268618176</v>
+        <v>0.0004021970241482642</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0007635977779184423</v>
+        <v>0.0005988009585787214</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.003472294868841168</v>
+        <v>-0.0006886885836600166</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0003822509205089763</v>
+        <v>0.001828775205730278</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001501697427289785</v>
+        <v>0.001682574199553243</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.199929286238468e-05</v>
+        <v>0.0004824327011784935</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.000460967196352171</v>
+        <v>0.0001629218714174074</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0008807960300904639</v>
+        <v>0.0005982270615283536</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0004110208112038339</v>
+        <v>0.001427487622554295</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0001060851416032115</v>
+        <v>0.0005217198150144163</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0001553347694150043</v>
+        <v>0.0009141635719283215</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.001678991180590094</v>
+        <v>-8.983222770851058e-05</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001254271720295881</v>
+        <v>0.001478782626270379</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0004854364352519613</v>
+        <v>0.0004592516495491361</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0005678504410732565</v>
+        <v>-0.0002603946131491952</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.0002802422356698474</v>
+        <v>0.0006644330438021285</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.001104481244452236</v>
+        <v>0.0008746057970967792</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.002199382481395953</v>
+        <v>-0.0006673079730448904</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.003139058152977427</v>
+        <v>-0.001706980950397968</v>
       </c>
       <c r="AV3" t="n">
-        <v>-3.976807485900468e-05</v>
+        <v>0.001656618305502467</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0007567611991880387</v>
+        <v>0.0009886713169097892</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0001795367016306037</v>
+        <v>4.52103331071463e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0001316919632959113</v>
+        <v>0.002643674497775304</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0009196912261431732</v>
+        <v>0.0008604300979967664</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.001535641858028926</v>
+        <v>-0.004371158463674719</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.002390596805137562</v>
+        <v>-0.0009368459964011691</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.521236544716475e-05</v>
+        <v>-0.0001465192280961514</v>
       </c>
       <c r="BD3" t="n">
-        <v>-9.976447507932807e-05</v>
+        <v>-0.0004719360178483911</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0004109135650159112</v>
+        <v>-0.0006385982513600108</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.001312376240639746</v>
+        <v>-0.003694386895503163</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002033814211504556</v>
+        <v>0.001035982344468897</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>4.16146483562252e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0006619491387334663</v>
+        <v>-0.0003817329985461382</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.001750876357581663</v>
+        <v>0.002269119684754837</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.001904018203699029</v>
+        <v>-0.002274971887570927</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.000162656857879272</v>
+        <v>0.0001862068275804995</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0003529389222086109</v>
+        <v>0.00135610251449815</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.004718408396704217</v>
+        <v>-0.002587902193750143</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0002794361949665557</v>
+        <v>-0.001496316504486489</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.002283297724278682</v>
+        <v>0.002268609348454636</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0001365511876097025</v>
+        <v>-1.913688017849079e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.002446206391352623</v>
+        <v>0.001650050473233253</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0002966732707574826</v>
+        <v>0.001068285597233676</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0001131704848718007</v>
+        <v>1.598291529902873e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.005714919748030771</v>
+        <v>0.006541709468939318</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001658404474143994</v>
+        <v>0.002842233653585722</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0003860635431771088</v>
+        <v>0.001199600482211632</v>
       </c>
       <c r="BX3" t="n">
-        <v>-2.986601798778631e-05</v>
+        <v>4.583490635485805e-06</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.097912274696471e-05</v>
+        <v>-0.0006977672208287099</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0002179241002508581</v>
+        <v>-3.898999706620555e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>7.830853563037811e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.001450012387484598</v>
+        <v>0.000220632772619196</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.00112779617804138</v>
+        <v>0.001014163898891933</v>
       </c>
       <c r="CD3" t="n">
-        <v>9.394685259316859e-05</v>
+        <v>-2.382157260144346e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>7.986121308361515e-05</v>
+        <v>-0.0002356261243092295</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0003918146535168676</v>
+        <v>-0.0002444524445399421</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.00114374019239078</v>
+        <v>0.002476642609897528</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0002173068985107273</v>
+        <v>0.0004281333453653424</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0004000388202715399</v>
+        <v>0.000502944818612242</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.003758518589021132</v>
+        <v>0.001238189263621213</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.003467284974039583</v>
+        <v>-0.0001062158570024363</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003472416276941052</v>
+        <v>0.003361255010780065</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01244297855108777</v>
+        <v>0.005808013517297584</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007966654564477789</v>
+        <v>0.007018936291240729</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004381975693033132</v>
+        <v>0.004013273282151408</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009051332844138402</v>
+        <v>0.006636406249256891</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009506791401178206</v>
+        <v>0.00960705430701978</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003770935203882087</v>
+        <v>0.0002889019660220381</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004857670198837722</v>
+        <v>0.005569884296195447</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02183419153870325</v>
+        <v>0.02218390404578413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01889588540824967</v>
+        <v>0.02029995729736542</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00300447535075642</v>
+        <v>0.003280878970474022</v>
       </c>
       <c r="N4" t="n">
-        <v>0.009641458385178851</v>
+        <v>0.007087310529537546</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00958337502302029</v>
+        <v>0.007078641247103545</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01270764851923042</v>
+        <v>0.0145472663440073</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01446603961973386</v>
+        <v>0.01705628103451928</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005044041919777469</v>
+        <v>0.004083604805245858</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003864221451782221</v>
+        <v>0.002476827918200508</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004286970419011532</v>
+        <v>0.004416699543795399</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003648652760198946</v>
+        <v>0.003392688013794007</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002306451435671814</v>
+        <v>0.0002982103148095851</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01239555039329611</v>
+        <v>0.009744279557196889</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003406447030720538</v>
+        <v>0.002211458145996732</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00331783689558276</v>
+        <v>0.001854206435255452</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00202787326243311</v>
+        <v>0.002792629765762512</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001805800829071691</v>
+        <v>0.003864618514294446</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006882899989860107</v>
+        <v>0.0007812033781950248</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006926876157377236</v>
+        <v>0.009741780000368093</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004546881578931057</v>
+        <v>0.005092913857985867</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002619967131059526</v>
+        <v>0.004560641338367205</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004230780209875435</v>
+        <v>0.005530751527459471</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006241011801632344</v>
+        <v>0.0005607513048082756</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.000791542802012726</v>
+        <v>0.0008168505181859301</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005278185718426196</v>
+        <v>0.004487073758595502</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.003465866165691868</v>
+        <v>0.004456047523863653</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0007741192957717287</v>
+        <v>0.001845562818122635</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0006310675607311575</v>
+        <v>0.0009901079933044602</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.00518017321679725</v>
+        <v>0.003951718033885025</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004989720409426323</v>
+        <v>0.005033322168633822</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0007862955923632962</v>
+        <v>0.001173233608934392</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002250818108996541</v>
+        <v>0.00379868034227354</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.003443591344736818</v>
+        <v>0.003155307563673348</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002038152932548097</v>
+        <v>0.005501160914198225</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.008183062853854834</v>
+        <v>0.003498323266721187</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.007946486133735773</v>
+        <v>0.005846740296216797</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003026821058438405</v>
+        <v>0.004133785812570745</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003359640664856679</v>
+        <v>0.004439446294800844</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0009146079446458167</v>
+        <v>0.0006972025814666121</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002983259876319734</v>
+        <v>0.002682100015127122</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.005773406490132284</v>
+        <v>0.00595134081743429</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004704461863678172</v>
+        <v>0.007458831966447102</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006974486059047714</v>
+        <v>0.004067374107059839</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001024086230556612</v>
+        <v>0.0008651008067979438</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0005860552409032125</v>
+        <v>0.001532063535746567</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001177582622277654</v>
+        <v>0.001715735540685993</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.005406862313973316</v>
+        <v>0.006846237299289401</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004028681870945379</v>
+        <v>0.008545598363212321</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1.315970728326537e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001749310900636351</v>
+        <v>0.001961175002876679</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002629582667371729</v>
+        <v>0.005197763602580497</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.006313570881307442</v>
+        <v>0.005200333143552805</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.00109762889214512</v>
+        <v>0.001311748219486969</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002793837001435303</v>
+        <v>0.005317404328998009</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.006651401717783839</v>
+        <v>0.006876149223131246</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.008627147657608346</v>
+        <v>0.004387593396170284</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003020899163127235</v>
+        <v>0.002586488366319893</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0002741024293543653</v>
+        <v>0.0004406716231567414</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.006155563269515619</v>
+        <v>0.004704388580362266</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003115165935712861</v>
+        <v>0.004190753754222002</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001802386596157261</v>
+        <v>0.001268447581638766</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.006626130528761632</v>
+        <v>0.008536390700956315</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.005214229360482859</v>
+        <v>0.002894118396032179</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.004107367082507203</v>
+        <v>0.003904529276650378</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0004338050831082891</v>
+        <v>0.0002989120502339221</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001202303291534727</v>
+        <v>0.0007136344121224554</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0007716834188479334</v>
+        <v>0.001079199558221016</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>2.476333328244442e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002803848346617656</v>
+        <v>0.001655149192978727</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.005470979865644218</v>
+        <v>0.003365989728867061</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0002176136978718714</v>
+        <v>4.964846816887798e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001460520418222547</v>
+        <v>0.00207115868061048</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003194801376798952</v>
+        <v>0.002597091688107293</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003724641064359809</v>
+        <v>0.004466344643325884</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.003103716567524288</v>
+        <v>0.001132559305087151</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003328551783479847</v>
+        <v>0.002258558677306529</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.007383724203890543</v>
+        <v>0.005070291532395917</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.009393277695780024</v>
+        <v>0.004634682905262578</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006493506493506518</v>
+        <v>-0.005192629815745397</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02517619420516833</v>
+        <v>-0.01151615575807785</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01064996084573218</v>
+        <v>-0.009827721221613161</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01033672670321063</v>
+        <v>-0.008077879038939506</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.02576350822239624</v>
+        <v>-0.01507439310884887</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01801914273824384</v>
+        <v>-0.01356637536412816</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.000768297614233715</v>
+        <v>-0.0003639304488475825</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.006089478044739005</v>
+        <v>-0.0119288313788921</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.007998324958123892</v>
+        <v>-0.008793969849246231</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.01358653093187157</v>
+        <v>-0.01239530988274706</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.00382854764877234</v>
+        <v>-0.005509527754763854</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02615505090054814</v>
+        <v>-0.01229444009397025</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.02028191072826934</v>
+        <v>-0.007781939242613412</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001431334622823976</v>
+        <v>-0.004118352658936475</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01793591344153138</v>
+        <v>-0.0169597989949749</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01101905550952773</v>
+        <v>-0.004084108370400385</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.009201252936570047</v>
+        <v>-0.003189726594863285</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008672294704528072</v>
+        <v>-0.007537688442211077</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.005778894472361773</v>
+        <v>-0.005054589567327183</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0004221028396009463</v>
+        <v>-0.0004604758250192021</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01467413034786084</v>
+        <v>-0.01143542582966819</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.006409719312945128</v>
+        <v>-0.003563038371182448</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.006742043551088739</v>
+        <v>-0.00319872051179535</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.004524507750314233</v>
+        <v>-0.002303182579564489</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004480737018425407</v>
+        <v>-0.006957217113154779</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001726784343822008</v>
+        <v>-0.0002913025384935652</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.009396241503398595</v>
+        <v>-0.01528583264291631</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01263608087091761</v>
+        <v>-0.008797653958944319</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.004059652029826</v>
+        <v>-0.003016338500209492</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.005906996229576888</v>
+        <v>-0.005725338491295873</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001487862176977273</v>
+        <v>-0.0004161464835622075</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001639344262295017</v>
+        <v>-0.0008510638297871909</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01307752545027404</v>
+        <v>-0.006744868035190654</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.004733975701717663</v>
+        <v>-0.005637636080870911</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0009196321471411139</v>
+        <v>-0.001205287713841363</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.00105716523101016</v>
+        <v>-0.0002913025384935652</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.0142742902838864</v>
+        <v>-0.006545153272576609</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.007708420611646438</v>
+        <v>-0.004398826979472192</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001885211562630951</v>
+        <v>-0.001639344262295128</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.00395458104933436</v>
+        <v>-0.006155778894472374</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.005488060326770028</v>
+        <v>-0.003760614638091453</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.00231980115990057</v>
+        <v>-0.007321848081440896</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.02027649769585257</v>
+        <v>-0.004608294930875623</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.02199413489736073</v>
+        <v>-0.01319648093841649</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.005559906029757223</v>
+        <v>-0.003278688524590223</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.005090054815974909</v>
+        <v>-0.007836865253898474</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001298701298701333</v>
+        <v>-0.001051354630004131</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004894283476898975</v>
+        <v>-0.00243902439024396</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.005442443226311644</v>
+        <v>-0.01119812059514487</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.009671104150352373</v>
+        <v>-0.01472200469851215</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01608713866778386</v>
+        <v>-0.008574979287489615</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001321928460342181</v>
+        <v>-0.001591956430666153</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0008285004142501662</v>
+        <v>-0.004231252618349446</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.003686635944700489</v>
+        <v>-0.005194805194805241</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.008168216740800639</v>
+        <v>-0.01706710853355425</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.008731401722787756</v>
+        <v>-0.01460454189506656</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.004528912252325057</v>
+        <v>-0.005739421868454164</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.00681284259984336</v>
+        <v>-0.003278688524590212</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01834939254294097</v>
+        <v>-0.01519185591229444</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001671850699844501</v>
+        <v>-0.001370399373531728</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003868471953578356</v>
+        <v>-0.007317073170731747</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01650607457059074</v>
+        <v>-0.01271384136858475</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01063651591289776</v>
+        <v>-0.008036785285885705</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.001047339757017207</v>
+        <v>-0.001121856866537674</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0004221028396009352</v>
+        <v>-0.0007870753935376729</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.007415165479681629</v>
+        <v>-0.004438224710116012</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.004225352112676051</v>
+        <v>-0.003812316715542585</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.004072043852779927</v>
+        <v>-0.003328112764291313</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.001252936570086127</v>
+        <v>-0.005877648940423874</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.007666527021365765</v>
+        <v>-0.002386934673366836</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.00582320904901551</v>
+        <v>-0.005613741097612113</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.001005446166736512</v>
+        <v>-0.0005446166736489677</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.00168363351605324</v>
+        <v>-0.001717637201508204</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.0008491710473109481</v>
+        <v>-0.002471721826560591</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.000768297614233715</v>
+        <v>-0.002669245647968999</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01280344557556773</v>
+        <v>-0.003198720511795339</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0.0001566170712607673</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.002819107282693789</v>
+        <v>-0.004815745393634852</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.006996229576874758</v>
+        <v>-0.004147465437788078</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.007477009196321449</v>
+        <v>-0.003995006242197263</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.007321848081440851</v>
+        <v>-0.0007439310884886474</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.005576362879733643</v>
+        <v>-0.003108211818879503</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.003984526112185705</v>
+        <v>-0.005918762088974805</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.02866537717601551</v>
+        <v>-0.01063829787234039</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.003121442449141803</v>
+        <v>-0.003963048091571686</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.006015686062331477</v>
+        <v>-0.002949638468809826</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.003814325575494013</v>
+        <v>-0.005194217312468833</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001746961906564565</v>
+        <v>-0.001305560730041769</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002659017009167128</v>
+        <v>-0.0003862192651719359</v>
       </c>
       <c r="H6" t="n">
-        <v>5.140796323586938e-05</v>
+        <v>-0.003665437924632825</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0003432058261739479</v>
+        <v>-0.0002453292689802156</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0001781179322110082</v>
+        <v>-0.001691701008188165</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0005409904286308997</v>
+        <v>-0.001070844712967583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001530930478806114</v>
+        <v>-0.00118893907973118</v>
       </c>
       <c r="M6" t="n">
-        <v>2.416531468732439e-06</v>
+        <v>-0.003852092349976275</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.008166037311661836</v>
+        <v>-0.002820481917216344</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.004923384790443386</v>
+        <v>-0.00166170864074861</v>
       </c>
       <c r="P6" t="n">
-        <v>0.006875570083206503</v>
+        <v>-0.000730155970414148</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.00460416208787986</v>
+        <v>-0.009993990023590627</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0003892217584383268</v>
+        <v>-0.002665166437313119</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002233647491824906</v>
+        <v>-0.001822753435361129</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.006048194423026309</v>
+        <v>-0.005872535897025619</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001633744046510352</v>
+        <v>-0.002239518963941631</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0001232346451794514</v>
+        <v>-0.0001740812379109835</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0002242055109256597</v>
+        <v>-0.003498755357043046</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.00104636102827827</v>
+        <v>-0.002109787947124906</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001468412993348794</v>
+        <v>-0.001108852322785514</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0009735353936548895</v>
+        <v>-0.001227442498864808</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001850045053526753</v>
+        <v>-0.002083456160329805</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0007950719043423454</v>
+        <v>-0.0001038922854115887</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.004913768405301911</v>
+        <v>-0.003179923370441362</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.004946306744775275</v>
+        <v>-0.003916625418261948</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.001916120413592781</v>
+        <v>-0.001023196729463735</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001264365184108854</v>
+        <v>-0.00198720000617054</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0001152506987140811</v>
+        <v>8.606615380924443e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0007600688495274565</v>
+        <v>-0.0005097320354527785</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.002296838976134802</v>
+        <v>-0.001517436145220641</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.001882853719283009</v>
+        <v>-0.0007934747497342354</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0003496938074721984</v>
+        <v>-0.0005335156567487592</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.00058412328407558</v>
+        <v>0.0001028860124982767</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.002321328544597862</v>
+        <v>-0.001903087575407286</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001695000472742</v>
+        <v>-0.0007888224288160633</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.000937515299916511</v>
+        <v>-0.0002016919740340267</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.002047237222921264</v>
+        <v>-0.001242412357717804</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.001563905804017357</v>
+        <v>-0.001587989721762925</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0001781210561876051</v>
+        <v>-0.002085317788167135</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.003847898786545601</v>
+        <v>-0.002728698307512511</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.005025427596548787</v>
+        <v>-0.005337485895390371</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0007754558171885528</v>
+        <v>-0.00178520804506935</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001736747872119224</v>
+        <v>-0.001606784565819647</v>
       </c>
       <c r="AX6" t="n">
-        <v>-9.363295880145949e-05</v>
+        <v>-0.0005596505116546497</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001945295183009615</v>
+        <v>0.002402251859579171</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.002870989933849469</v>
+        <v>-0.001628419860089356</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.004926424014533468</v>
+        <v>-0.007934189111445455</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.003512929674692025</v>
+        <v>-0.002949320572901959</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0002548760534535066</v>
+        <v>-0.0005600470398461982</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0005521129367185129</v>
+        <v>-0.0009583266903507525</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0003440719231688788</v>
+        <v>-0.0002715255189555482</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.005710198934748612</v>
+        <v>-0.006355260277087169</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.004775755668398812</v>
+        <v>-0.0029776807433113</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0004911725817067474</v>
+        <v>-0.000396023282607963</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.002506573728262163</v>
+        <v>-0.0008888204024701195</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.002331459357389218</v>
+        <v>-0.003213102799749581</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0002904378442838418</v>
+        <v>-0.0007462580814560027</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002161407117889591</v>
+        <v>-0.001903661043461172</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.005810796806515339</v>
+        <v>-0.006345305047341041</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.004344840357146262</v>
+        <v>-0.004591140707489446</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0004863456341469313</v>
+        <v>6.480887729118647e-05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.720062208393166e-06</v>
+        <v>-0.0001117899363899971</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0002499246450745257</v>
+        <v>-0.001630418311955684</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001763248868455761</v>
+        <v>-0.001896705752822678</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0005707654587174509</v>
+        <v>0.0004229601084241114</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0005839623949415535</v>
+        <v>0.002826067377405261</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001117480598272502</v>
+        <v>0.0009713921585331381</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0005234017417309472</v>
+        <v>-0.001426798344992555</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0001098428400576723</v>
+        <v>-0.0001664111865139595</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0008194534925860947</v>
+        <v>-0.001320370873155474</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0004296882423015181</v>
+        <v>-0.0002511759359601878</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.000421081346606006</v>
+        <v>-0.000780682182295625</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001420008284032895</v>
+        <v>-0.001523155106792312</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-2.998800479808161e-05</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0007540846250523814</v>
+        <v>-0.000994200497100231</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0003226083385825307</v>
+        <v>-0.001278797112557106</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0004389141297144933</v>
+        <v>-0.001128996301945825</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0009263209743491291</v>
+        <v>-0.000453276866531796</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002258677593059952</v>
+        <v>-0.0008311382832926706</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.001373151653295998</v>
+        <v>-0.003103372996671355</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.003660437793881205</v>
+        <v>-0.001067144331547137</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003870819694975324</v>
+        <v>0.0001365636603504417</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.004218685776078368</v>
+        <v>-0.001105455971619324</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005994442534885569</v>
+        <v>0.0004069688904195457</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0005708544064072895</v>
+        <v>8.524999283613942e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007268983590191291</v>
+        <v>0.0005116911404265234</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00306810401811281</v>
+        <v>0.00326167888365404</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.733763157477869e-05</v>
+        <v>5.551115123125783e-18</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001121884061305495</v>
+        <v>-0.000244873626676223</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004312132013732234</v>
+        <v>0.004598372769063136</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006678940716206117</v>
+        <v>0.004094746238363101</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001199801267106471</v>
+        <v>-0.0007410712679530918</v>
       </c>
       <c r="N7" t="n">
-        <v>1.931204727857478e-05</v>
+        <v>-0.0003370142576453627</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003962779979455821</v>
+        <v>0.00101127366170472</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00974242058518025</v>
+        <v>0.002837762183073717</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004545787869665335</v>
+        <v>0.004981231192880003</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0005373351008936822</v>
+        <v>-0.001003818253096539</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0009840274128292358</v>
+        <v>0.0005483772138400067</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0009205432184772434</v>
+        <v>-0.001093990337481771</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001575561678195725</v>
+        <v>0.001515058764074379</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.080732417809594e-05</v>
+        <v>8.057928852771014e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003813922152435184</v>
+        <v>-0.0007052749996393993</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001705471013241178</v>
+        <v>-0.0003098343309471118</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0003286642489953695</v>
+        <v>0.0003888605343872531</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0007912143607439915</v>
+        <v>0.0004093092905721629</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.001224492006674854</v>
+        <v>0.0001358641195515375</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0005131695377836532</v>
+        <v>0.0002560328901098808</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0002485501242750765</v>
+        <v>0.001866227821284022</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.002221263740677615</v>
+        <v>-0.0009859186721611513</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001272074966700309</v>
+        <v>0.0006440225520961962</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.002508698947985444</v>
+        <v>0.0002426511590587432</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001206310844040992</v>
+        <v>0.0006124805731226257</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0003888605343872642</v>
+        <v>2.021835826928053e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0005334133595119528</v>
+        <v>0.001286575940678608</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0001905380926945033</v>
+        <v>0.0003721543208512035</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.230190270490322e-06</v>
+        <v>0.0004069438993397123</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0001241888103409417</v>
+        <v>0.0009243856036234509</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.001268166910238072</v>
+        <v>0.0002464957465982354</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.001878496478481018</v>
+        <v>0.0003009162511461605</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0004781871304845531</v>
+        <v>0.0002072199173844158</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0006968476356973008</v>
+        <v>-0.0005399474765904521</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.61592255328947e-05</v>
+        <v>0.001017757422112176</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.001183279106152524</v>
+        <v>-0.0006195460474273772</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.001545698345218905</v>
+        <v>-0.002226950578852404</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.003693884143371073</v>
+        <v>-0.0007607597501453455</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0001368614827854609</v>
+        <v>0.001199871520665791</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001502711508776883</v>
+        <v>0.001509046949663179</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.761165055636179e-05</v>
+        <v>0.000214878924704176</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.000228566727214996</v>
+        <v>0.003147934268051306</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.000123516551562658</v>
+        <v>2.07689210206198e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0001966839295368893</v>
+        <v>-0.006219651295973077</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.001803300167068317</v>
+        <v>-0.001052977481783701</v>
       </c>
       <c r="BC7" t="n">
-        <v>-6.281407035175213e-05</v>
+        <v>-0.0002026362928343073</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0002597257220909755</v>
+        <v>0.0002403691650631257</v>
       </c>
       <c r="BE7" t="n">
-        <v>-1.944012441681409e-05</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.001684936122082503</v>
+        <v>-0.002278562897526037</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.002155668262415983</v>
+        <v>-0.0006957293067739955</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.0002808716131180278</v>
+        <v>9.739615138181222e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.001631157774093822</v>
+        <v>0.001016602318356796</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0006401554006696454</v>
+        <v>-0.002613899850492513</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001665534072467723</v>
+        <v>9.593246354566709e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.001145753859846105</v>
+        <v>0.0008931223134642898</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.003726764712688057</v>
+        <v>-0.00259185232746979</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.001300260036862522</v>
+        <v>-0.002038524275998532</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.001964776023270792</v>
+        <v>0.002563531912222222</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.33687676746686e-05</v>
+        <v>-8.05510489593214e-07</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.002396340482514042</v>
+        <v>0.0007299228737535802</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0002959015479818749</v>
+        <v>-0.000220720336696273</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0001549691165524336</v>
+        <v>0.0004983328282342659</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.004059345642129802</v>
+        <v>0.005675432391674872</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.001536187575268882</v>
+        <v>0.003693162753482276</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.000544851884091313</v>
+        <v>0.001876556617480174</v>
       </c>
       <c r="BX7" t="n">
-        <v>5.98182722841678e-05</v>
+        <v>5.836498861698236e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.198489629570144e-05</v>
+        <v>-0.0004326779926327295</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0002207442758602907</v>
+        <v>0.0001268198340164561</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0007719857179995626</v>
+        <v>4.156849189155266e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001929208974050689</v>
+        <v>0.0006710985864703644</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.000514070999744054</v>
+        <v>0.0002626817245897417</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.001309825117160035</v>
+        <v>-0.0005774651859790814</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.001377596471747045</v>
+        <v>0.001636307227332873</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0003299302363036327</v>
+        <v>0.0002004088385403335</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0003872444037973599</v>
+        <v>0.0004884598318192268</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.002201452234036388</v>
+        <v>0.0009535454869373905</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0002540024581601019</v>
+        <v>4.664686546268504e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001875471849371269</v>
+        <v>0.001251262938563177</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003968749164356552</v>
+        <v>0.002554819893103674</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006268286546000781</v>
+        <v>0.003930238141946679</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002528498709380966</v>
+        <v>0.002880938952124434</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003747059559070654</v>
+        <v>0.00365435263408802</v>
       </c>
       <c r="H8" t="n">
-        <v>0.007072952613826325</v>
+        <v>0.008748622929022499</v>
       </c>
       <c r="I8" t="n">
-        <v>-9.671179883938284e-06</v>
+        <v>0.0001542549504966295</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004219984604282278</v>
+        <v>0.002963834043516461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007147058051225216</v>
+        <v>0.0113970585949135</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01300220126837985</v>
+        <v>0.01016772218621268</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00285827703662849</v>
+        <v>0.002180083140602113</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00221964599073331</v>
+        <v>0.00266375554977539</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006249578090841581</v>
+        <v>0.005289359969123575</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01879545320618461</v>
+        <v>0.01362477623419425</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01645404683983999</v>
+        <v>0.0131420314191514</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001644889553886839</v>
+        <v>0.001019447103246809</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0008437685387299831</v>
+        <v>0.0008085446451806144</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0006921343741135982</v>
+        <v>0.0001592129105804641</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002407735104999783</v>
+        <v>0.002996396396691911</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001368591047700512</v>
+        <v>0.0001675568177431891</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008615957431669548</v>
+        <v>0.009785165031631095</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002699518489648905</v>
+        <v>0.0004740850441945166</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001956322985844488</v>
+        <v>0.0009040101970781312</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001247194905614085</v>
+        <v>0.001527351356881104</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.0002585805111014472</v>
+        <v>0.002591385554434261</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0002086883369163905</v>
+        <v>0.0004075597419125887</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006604045287103228</v>
+        <v>0.002570586586864917</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.001112022859427827</v>
+        <v>0.001778142768365249</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002311036387890941</v>
+        <v>0.002541695681905154</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.004014054008929618</v>
+        <v>0.004566274830698122</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.000523449986024549</v>
+        <v>0.0008425344939072543</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.0001940101855723991</v>
+        <v>0.0006179953191401882</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002632384167238916</v>
+        <v>0.002743358782649455</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.003516752996832423</v>
+        <v>0.003151782643146575</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0005202528408028927</v>
+        <v>0.0006942826983551392</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002198816573314305</v>
+        <v>0.001492377087751851</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0009342534056993979</v>
+        <v>0.001728919604845994</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.003899472787479416</v>
+        <v>0.00242253624560021</v>
       </c>
       <c r="AP8" t="n">
-        <v>-8.200631524333536e-05</v>
+        <v>0.001374454663125563</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.099604988337723e-05</v>
+        <v>0.001385612398234023</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0003111402679082914</v>
+        <v>0.002356101412215058</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.00270071292572856</v>
+        <v>0.002977698740361365</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00242236576786023</v>
+        <v>0.0003380532966874156</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001767513506113855</v>
+        <v>0.003452144411656902</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.00157733840131902</v>
+        <v>0.003225261444134411</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.003011207588943235</v>
+        <v>0.004578632303871277</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0001209706170099717</v>
+        <v>0.000659514676569159</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.00222906220776925</v>
+        <v>0.004376364275672557</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003566489750991347</v>
+        <v>0.004740360409397102</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001886355463568934</v>
+        <v>-0.0003465425508981017</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002521082894547447</v>
+        <v>0.0006434508229373581</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0002597970692720053</v>
+        <v>0.0003975080237136747</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.000269013653172609</v>
+        <v>0.0005461636879625559</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.840258160673574e-05</v>
+        <v>7.292324948640627e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002502358492781465</v>
+        <v>-0.0004958622804666051</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001715035853424465</v>
+        <v>0.00655679738944343</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0.0002153198372680382</v>
+        <v>0.0004665900332115447</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0.0005304176898687258</v>
+        <v>0.003364357464351311</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001327760384357635</v>
+        <v>0.0012667756535794</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001013248695192392</v>
+        <v>0.0003482359474004937</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.00114373913304314</v>
+        <v>0.003850255933728811</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0.001254810995081918</v>
+        <v>0.002378158603240121</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002030974282386339</v>
+        <v>0.00108965298480122</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.004516463272525353</v>
+        <v>0.003710699772033096</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0003969203931838527</v>
+        <v>0.000333544286873022</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.003812784401820154</v>
+        <v>0.002910334780343585</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.00292513378360483</v>
+        <v>0.002213524728356017</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0008610059121393759</v>
+        <v>0.0005734999518067135</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.009608473201472506</v>
+        <v>0.009100074065371931</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.004450922167433977</v>
+        <v>0.005308010067725175</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0015521562111392</v>
+        <v>0.003993932072264217</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0002155062586235462</v>
+        <v>8.00951992247223e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0005552054129630336</v>
+        <v>-0.0002435354912114135</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0006848193848432244</v>
+        <v>0.0007329652864746545</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.002244534178400423</v>
+        <v>0.001432767112227665</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.00233854843831294</v>
+        <v>0.004277036751659902</v>
       </c>
       <c r="CD8" t="n">
-        <v>8.809710258417535e-05</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0008241493449276632</v>
+        <v>0.0003496938074721956</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002303028542242147</v>
+        <v>0.001321045510290339</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.002990702885320329</v>
+        <v>0.006023404047892833</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001813103166747188</v>
+        <v>0.001088176362048049</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001477095120351576</v>
+        <v>0.002103201467231852</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.005799103747897091</v>
+        <v>0.004605078165031232</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001636747761617807</v>
+        <v>0.003315945340348889</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003453568687643849</v>
+        <v>0.003615863141524101</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01825795644891127</v>
+        <v>0.008123953098827463</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01605754276827369</v>
+        <v>0.01164641809803095</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00439698492462316</v>
+        <v>0.005764023210831759</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005197920831667357</v>
+        <v>0.009090909090909049</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01277219430485765</v>
+        <v>0.01463809138697931</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006700167504188004</v>
+        <v>0.0004189359028068273</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01024558710667687</v>
+        <v>0.008322929671244284</v>
       </c>
       <c r="K9" t="n">
         <v>0.06640430820215412</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05472245236122619</v>
+        <v>0.04610604805302404</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007008613938919372</v>
+        <v>0.003265940902021769</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005103607060629267</v>
+        <v>0.01535769828926906</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01143079315707617</v>
+        <v>0.01535769828926905</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04212924606462306</v>
+        <v>0.03965785381026439</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02962674961119748</v>
+        <v>0.04016329704510108</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009823484267075921</v>
+        <v>0.008169250104733928</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002669245647969032</v>
+        <v>0.004411152725759482</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003771384136858436</v>
+        <v>0.005053852526926273</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005443234836702926</v>
+        <v>0.00406753645433613</v>
       </c>
       <c r="V9" t="n">
-        <v>0.000414250207125133</v>
+        <v>0.000544323483670317</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02674961119751164</v>
+        <v>0.01726647796198943</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004432348367029515</v>
+        <v>0.004038384646141491</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003367267032106503</v>
+        <v>0.003300076745970848</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002345058626465724</v>
+        <v>0.005909439754412893</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001683633516053273</v>
+        <v>0.004943443653121016</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000464216634429393</v>
+        <v>0.002270947533281131</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01143695014662752</v>
+        <v>0.01688311688311683</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.00187924830067977</v>
+        <v>0.008809710258418157</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.003518592562974843</v>
+        <v>0.01111975116640748</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.008009331259720032</v>
+        <v>0.01294712286158631</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006189555125725055</v>
+        <v>0.001173020527859181</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001035625517812788</v>
+        <v>0.001632970451010907</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00414428242517263</v>
+        <v>0.007270606531881807</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.005403288958496499</v>
+        <v>0.01080657791699297</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001591289782244609</v>
+        <v>0.005318257956448902</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007906783187682342</v>
+        <v>0.002806870548805995</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.005755677368833223</v>
+        <v>0.005823209049015443</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01000837520938029</v>
+        <v>0.01178071539657853</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001046901172529369</v>
+        <v>0.002036021926389997</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.003435274403016297</v>
+        <v>0.007400156617071274</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.005676516329704473</v>
+        <v>0.005754276827371696</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.004182655410590897</v>
+        <v>0.01232503888024885</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.009866558835422567</v>
+        <v>0.006462303231151645</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.006600153491941629</v>
+        <v>0.004528012279355342</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.004524507750314178</v>
+        <v>0.008492129246064651</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.005782450465022282</v>
+        <v>0.006048053024026556</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001934235976789156</v>
+        <v>0.0008797653958943829</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.004733975701717597</v>
+        <v>0.005571847507331329</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01402847571189284</v>
+        <v>0.01014913007456504</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.004438860971524317</v>
+        <v>0.009154929577464809</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.006648522550544289</v>
+        <v>0.006259720062208385</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001719312275090001</v>
+        <v>0.001096319498825393</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0009671179883945835</v>
+        <v>0.000690713737528803</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0002913025384935763</v>
+        <v>0.0004221028396009352</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.006638526477359874</v>
+        <v>0.008087091757387244</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.003017408123791076</v>
+        <v>0.01371168185584095</v>
       </c>
       <c r="BH9" t="n">
+        <v>4.161464835622519e-05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.001201325600662817</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0150397989107666</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.003231151615575834</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.002941176470588225</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.01156263091746959</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.007676929228308616</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.00534382767191387</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.007202680067001688</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.0005090054815974799</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.00996649916247907</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.008740679370339722</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0008491710473109481</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.02684341342170673</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.00578443612151478</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.006227254346946954</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0005873140172278802</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0004043671653861658</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.001083172147001976</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>7.83085356303781e-05</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.002740798747063433</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.00485240598463399</v>
+      </c>
+      <c r="CD9" t="n">
         <v>0</v>
       </c>
-      <c r="BI9" t="n">
-        <v>0.001779497098645999</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.002261306532663365</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.004278288684526221</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.001758793969849282</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.005661140315406432</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.00352112676056342</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.02080093312597198</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.007723412858875877</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.0004398240703718637</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.01435503437120909</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.004082426127527195</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.002304892842701156</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.02013256006628005</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.01005025125628145</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.009017387788111609</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.0004161464835622519</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.002587949858471506</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.001527016444792506</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.00862646566164158</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.004488475535786541</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.0006963249516440673</v>
-      </c>
       <c r="CE9" t="n">
-        <v>0.001940962393853596</v>
+        <v>0.003367267032106525</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.003685092127303236</v>
+        <v>0.00460978568540229</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.00595144870790919</v>
+        <v>0.009174696271470417</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.003433835845896216</v>
+        <v>0.002628386575010078</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.005276381909547767</v>
+        <v>0.003993735317149583</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01762981574539366</v>
+        <v>0.009162098668754903</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002122347066167318</v>
+        <v>0.005525709900230213</v>
       </c>
     </row>
   </sheetData>
